--- a/excel-files/NAVOTAS/NAVOTAS ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/NAVOTAS ELEMENTARY SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41D5D0BF-878C-4CFF-9DDB-63AC440A46FD}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AE30DFE-BFEC-4881-A243-5DA21B7A6D31}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Math</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Science</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -742,6 +742,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -753,12 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3711,17 +3711,25 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>197</v>
+      </c>
+      <c r="D11" s="1">
+        <v>238</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3814,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3884,7 +3892,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3904,7 +3912,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>261</v>
@@ -3916,7 +3924,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
@@ -3944,7 +3952,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -3972,7 +3980,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -3990,17 +3998,25 @@
       <c r="B25" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+      <c r="C25" s="1">
+        <v>261</v>
+      </c>
+      <c r="D25" s="1">
+        <v>361</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="33.75" customHeight="1">
@@ -4008,19 +4024,27 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="1">
+        <v>261</v>
+      </c>
+      <c r="D26" s="1">
+        <v>361</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="33.75" customHeight="1">
@@ -4030,17 +4054,25 @@
       <c r="B27" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+      <c r="C27" s="1">
+        <v>261</v>
+      </c>
+      <c r="D27" s="1">
+        <v>361</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27.75" customHeight="1">
@@ -4070,17 +4102,25 @@
       <c r="B29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>261</v>
+      </c>
+      <c r="D29" s="1">
+        <v>361</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4098,19 +4138,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="C31" s="1">
+        <v>261</v>
+      </c>
+      <c r="D31" s="1">
+        <v>325</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4118,7 +4166,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4190,7 +4238,7 @@
         <v>2025</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
@@ -4206,19 +4254,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
+        <v>261</v>
+      </c>
+      <c r="D36" s="1">
+        <v>325</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4228,17 +4284,25 @@
       <c r="B37" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+      <c r="C37" s="1">
+        <v>261</v>
+      </c>
+      <c r="D37" s="1">
+        <v>325</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4248,17 +4312,25 @@
       <c r="B38" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>261</v>
+      </c>
+      <c r="D38" s="1">
+        <v>325</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4296,7 +4368,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4316,7 +4388,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4396,7 +4468,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4486,7 +4558,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4506,7 +4578,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4586,7 +4658,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4676,7 +4748,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4696,7 +4768,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4776,7 +4848,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4866,7 +4938,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4886,7 +4958,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -4966,7 +5038,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5056,7 +5128,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5076,7 +5148,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5156,7 +5228,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5408,10 +5480,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E91:E98 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E2:E6 E21:E29 E14:E19 E8:E12 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F21:F29" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F21:F29 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5424,7 +5496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5454,38 +5526,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5524,10 +5596,10 @@
       <c r="L2" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5560,10 +5632,10 @@
       <c r="X2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>60</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -5999,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6068,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6572,7 +6644,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1">
         <v>197</v>
@@ -6655,7 +6727,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>197</v>
@@ -6810,7 +6882,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7022,7 +7094,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>215</v>
@@ -7245,7 +7317,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
         <v>215</v>
@@ -7322,7 +7394,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="5">
@@ -7474,7 +7546,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7543,7 +7615,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7819,7 +7891,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -8109,7 +8181,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1">
         <v>261</v>
@@ -8186,7 +8258,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -8476,7 +8548,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1">
         <v>261</v>
@@ -8774,7 +8846,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8843,7 +8915,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -9119,7 +9191,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9409,7 +9481,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9478,7 +9550,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9754,7 +9826,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -10044,7 +10116,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10113,7 +10185,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10389,7 +10461,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10679,7 +10751,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10748,7 +10820,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -11024,7 +11096,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11314,7 +11386,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11383,7 +11455,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11659,7 +11731,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -13494,186 +13566,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13701,8 +13593,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 X112:X127 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 F23:F31" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G103:G110 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G23:G31" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13720,7 +13612,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13750,38 +13642,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13820,10 +13712,10 @@
       <c r="L2" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -13856,10 +13748,10 @@
       <c r="X2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -14216,7 +14108,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14285,7 +14177,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14349,7 +14241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14777,7 +14669,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
         <v>197</v>
@@ -14854,7 +14746,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1">
         <v>197</v>
@@ -15208,7 +15100,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15423,7 +15315,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1">
         <v>215</v>
@@ -15500,7 +15392,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
         <v>215</v>
@@ -15647,7 +15539,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15716,7 +15608,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15992,7 +15884,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -16407,7 +16299,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16476,7 +16368,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16752,7 +16644,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -17167,7 +17059,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
         <v>218</v>
@@ -17262,7 +17154,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
         <v>218</v>
@@ -17618,7 +17510,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1">
         <v>218</v>
@@ -18097,7 +17989,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -18166,7 +18058,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18442,7 +18334,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18857,7 +18749,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18883,11 +18775,11 @@
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
-        <f t="shared" ref="N74:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
+        <f t="shared" ref="N79:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
         <v>0</v>
       </c>
       <c r="O79" s="12">
-        <f t="shared" ref="O74:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
+        <f t="shared" ref="O79:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
         <v>0</v>
       </c>
       <c r="P79" s="12">
@@ -18926,7 +18818,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -19202,7 +19094,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19617,7 +19509,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19686,7 +19578,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19962,7 +19854,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -20377,7 +20269,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20446,7 +20338,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20722,7 +20614,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -22195,186 +22087,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101 C55:C65" name="Textbooks"/>
@@ -22392,8 +22104,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 M115:M122 Y12:Y19 S12:S19 M12:M19 M21:M29 G12:G19 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G21:G29 S55:S65 M55:M65 G55:G65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 Y55:Y65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 R55:R65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 F55:F65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 L55:L65 R91:R101 R103:R113 R12:R19 R3:R10 F12:F19 F31:F41 F43:F53 F67:F77 F79:F89 F21:F29 F3:F10 F91:F101 X115:X122 F103:F113 F115:F122 R115:R122 L115:L122 X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
